--- a/data/trans_camb/IP19C08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 1,2</t>
+          <t>-11,75; 1,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 8,67</t>
+          <t>-7,44; 7,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 2,92</t>
+          <t>-11,11; 2,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 3,4</t>
+          <t>-8,35; 3,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 5,86</t>
+          <t>-7,6; 5,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -1,6</t>
+          <t>-11,22; -1,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 0,9</t>
+          <t>-7,5; 1,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,8</t>
+          <t>-5,34; 4,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -0,75</t>
+          <t>-9,03; -0,68</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,06; 53,84</t>
+          <t>-90,92; 78,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 223,76</t>
+          <t>-65,39; 174,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,55; 76,77</t>
+          <t>-86,97; 75,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,24; 124,3</t>
+          <t>-81,86; 120,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,52; 171,51</t>
+          <t>-75,13; 140,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -15,08</t>
+          <t>-100,0; -9,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,66; 26,26</t>
+          <t>-75,73; 35,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,29; 94,36</t>
+          <t>-54,74; 107,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,36; -8,43</t>
+          <t>-86,47; -5,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 1,81</t>
+          <t>-7,36; 1,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 1,63</t>
+          <t>-7,46; 1,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 0,44</t>
+          <t>-8,37; 0,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 2,95</t>
+          <t>-6,43; 2,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -0,36</t>
+          <t>-8,16; -0,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,46</t>
+          <t>-7,11; 1,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,64</t>
+          <t>-5,79; 0,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -0,58</t>
+          <t>-6,47; -0,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -0,17</t>
+          <t>-6,11; 0,39</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,73; 68,8</t>
+          <t>-82,39; 46,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,4; 54,16</t>
+          <t>-85,96; 40,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,17; 48,37</t>
+          <t>-90,7; 43,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,52; 110,86</t>
+          <t>-82,36; 107,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 10,48</t>
+          <t>-100,0; 18,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,67; 76,86</t>
+          <t>-85,19; 80,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,24; 16,65</t>
+          <t>-72,46; 30,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,76; -3,46</t>
+          <t>-82,18; -7,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,05; 7,0</t>
+          <t>-80,49; 22,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 4,33</t>
+          <t>-8,01; 4,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 3,51</t>
+          <t>-7,88; 3,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -0,91</t>
+          <t>-10,82; -1,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 0,69</t>
+          <t>-8,49; 0,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 2,42</t>
+          <t>-6,81; 2,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 11,56</t>
+          <t>-5,22; 12,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 1,12</t>
+          <t>-6,63; 0,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 1,74</t>
+          <t>-6,28; 1,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 4,51</t>
+          <t>-6,26; 3,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,85; 163,88</t>
+          <t>-85,08; 209,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 156,85</t>
+          <t>-80,6; 135,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 24,02</t>
+          <t>-100,0; 14,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 272,13</t>
+          <t>-100,0; 75,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,44</t>
+          <t>-90,63; 164,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-89,15; 706,15</t>
+          <t>-87,04; 903,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,73; 47,11</t>
+          <t>-82,02; 41,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,28; 67,33</t>
+          <t>-76,33; 53,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,55; 159,07</t>
+          <t>-87,92; 143,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,78</t>
+          <t>-2,12; 7,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,34</t>
+          <t>-5,07; 1,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,95</t>
+          <t>-5,88; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 8,61</t>
+          <t>-0,67; 8,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,97</t>
+          <t>-3,69; 1,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 6,41</t>
+          <t>-1,38; 6,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,24</t>
+          <t>-0,49; 6,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,17</t>
+          <t>-3,56; 1,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,01</t>
+          <t>-2,32; 2,95</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,82; —</t>
+          <t>-63,59; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,62; —</t>
+          <t>-47,66; 1142,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,95; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 519,06</t>
+          <t>-26,7; 516,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-91,17; 237,8</t>
+          <t>-100,0; 195,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,38; 297,78</t>
+          <t>-68,81; 323,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,29</t>
+          <t>-4,28; 1,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,75</t>
+          <t>-4,53; 0,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -1,4</t>
+          <t>-6,07; -1,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,32</t>
+          <t>-3,75; 1,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,21</t>
+          <t>-4,47; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,58</t>
+          <t>-4,01; 1,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,52</t>
+          <t>-3,16; 0,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,23</t>
+          <t>-3,82; -0,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,34</t>
+          <t>-4,17; -0,36</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 31,32</t>
+          <t>-59,58; 26,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 19,33</t>
+          <t>-62,9; 22,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,87; -28,99</t>
+          <t>-81,98; -27,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 41,08</t>
+          <t>-58,44; 38,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 10,55</t>
+          <t>-72,14; 9,23</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 49,33</t>
+          <t>-65,86; 62,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 13,32</t>
+          <t>-50,89; 11,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-59,72; -4,41</t>
+          <t>-60,35; -5,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-65,0; -5,12</t>
+          <t>-67,38; -7,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 1,63</t>
+          <t>-11,64; 0,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 7,62</t>
+          <t>-7,8; 8,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 2,92</t>
+          <t>-10,26; 3,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 3,85</t>
+          <t>-8,46; 3,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 5,58</t>
+          <t>-7,89; 4,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -1,5</t>
+          <t>-11,69; -1,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 1,54</t>
+          <t>-7,9; 1,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 4,65</t>
+          <t>-5,63; 4,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; -0,68</t>
+          <t>-9,23; -1,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,92; 78,12</t>
+          <t>-90,79; 70,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,39; 174,28</t>
+          <t>-66,48; 226,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,97; 75,87</t>
+          <t>-81,59; 103,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-81,86; 120,14</t>
+          <t>-82,51; 101,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,13; 140,34</t>
+          <t>-75,04; 140,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,49</t>
+          <t>-100,0; -14,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,73; 35,47</t>
+          <t>-80,96; 24,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 107,91</t>
+          <t>-55,18; 92,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,47; -5,64</t>
+          <t>-85,7; -9,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 1,31</t>
+          <t>-7,41; 1,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,16</t>
+          <t>-7,48; 1,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 0,57</t>
+          <t>-8,65; 0,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,67</t>
+          <t>-6,44; 2,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; -0,15</t>
+          <t>-7,7; -0,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 1,47</t>
+          <t>-6,56; 1,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 0,81</t>
+          <t>-5,56; 0,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -0,55</t>
+          <t>-6,34; -0,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,39</t>
+          <t>-6,39; -0,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,39; 46,8</t>
+          <t>-81,88; 82,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,96; 40,93</t>
+          <t>-82,93; 48,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,7; 43,99</t>
+          <t>-91,83; 42,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,36; 107,27</t>
+          <t>-78,78; 97,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,25</t>
+          <t>-92,68; 39,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,19; 80,68</t>
+          <t>-85,1; 98,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,46; 30,31</t>
+          <t>-72,76; 24,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,18; -7,31</t>
+          <t>-82,61; -8,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-80,49; 22,34</t>
+          <t>-82,44; 7,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 4,85</t>
+          <t>-7,07; 4,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,36</t>
+          <t>-8,3; 3,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -1,1</t>
+          <t>-10,54; -0,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 0,62</t>
+          <t>-9,16; 0,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 2,61</t>
+          <t>-7,61; 2,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 12,43</t>
+          <t>-5,72; 10,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 0,99</t>
+          <t>-6,08; 1,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1,45</t>
+          <t>-6,08; 1,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 3,97</t>
+          <t>-6,17; 4,52</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,08; 209,27</t>
+          <t>-79,65; 176,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,6; 135,2</t>
+          <t>-85,52; 127,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,16</t>
+          <t>-100,0; 33,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,72</t>
+          <t>-100,0; 51,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,63; 164,18</t>
+          <t>-100,0; 126,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,04; 903,35</t>
+          <t>-92,29; 847,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,02; 41,37</t>
+          <t>-81,17; 61,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,33; 53,17</t>
+          <t>-78,13; 78,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-87,92; 143,51</t>
+          <t>-86,36; 166,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 7,77</t>
+          <t>-1,8; 7,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,45</t>
+          <t>-5,17; 1,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 0,97</t>
+          <t>-5,81; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 8,65</t>
+          <t>-0,69; 7,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,99</t>
+          <t>-4,28; 1,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,28</t>
+          <t>-1,87; 6,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,22</t>
+          <t>-0,51; 6,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,13</t>
+          <t>-3,8; 1,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,95</t>
+          <t>-2,24; 3,22</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,59; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 1142,08</t>
+          <t>-56,34; 1063,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,48; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 516,7</t>
+          <t>-24,83; 550,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 195,57</t>
+          <t>-92,17; 253,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,81; 323,49</t>
+          <t>-67,59; 342,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,06</t>
+          <t>-4,36; 0,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,87</t>
+          <t>-4,54; 0,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -1,31</t>
+          <t>-5,87; -1,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,27</t>
+          <t>-3,61; 1,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,12</t>
+          <t>-4,63; 0,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,87</t>
+          <t>-3,99; 1,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,43</t>
+          <t>-3,17; 0,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,34</t>
+          <t>-3,81; -0,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,36</t>
+          <t>-4,23; -0,51</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 26,06</t>
+          <t>-60,84; 24,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-62,9; 22,04</t>
+          <t>-62,76; 18,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,98; -27,66</t>
+          <t>-81,15; -26,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 38,3</t>
+          <t>-58,58; 46,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 9,23</t>
+          <t>-73,75; 2,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 62,66</t>
+          <t>-66,02; 53,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 11,28</t>
+          <t>-50,27; 13,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,35; -5,23</t>
+          <t>-60,15; -3,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-67,38; -7,5</t>
+          <t>-68,31; -6,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,01</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-4,64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,11</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,77</t>
+          <t>-3,68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,7</t>
+          <t>-4,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 0,66</t>
+          <t>-8,91; 3,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 8,13</t>
+          <t>-7,13; 5,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 3,43</t>
+          <t>-11,74; -2,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 3,27</t>
+          <t>-11,83; 1,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 4,83</t>
+          <t>-7,67; 8,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,69; -1,52</t>
+          <t>-11,3; 2,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 1,02</t>
+          <t>-8,0; 0,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 4,53</t>
+          <t>-5,57; 4,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; -1,09</t>
+          <t>-9,45; -1,04</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-34,82%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-15,98%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-86,54%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-55,42%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-39,56%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-34,82%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,98%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-83,09%</t>
+          <t>-43,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-61,69%</t>
+          <t>-64,26%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,79; 70,66</t>
+          <t>-86,24; 124,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 226,2</t>
+          <t>-75,52; 171,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 103,17</t>
+          <t>-100,0; -32,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,51; 101,68</t>
+          <t>-90,06; 53,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,04; 140,08</t>
+          <t>-64,29; 223,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -14,66</t>
+          <t>-87,68; 67,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,96; 24,33</t>
+          <t>-76,66; 26,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 92,71</t>
+          <t>-57,29; 94,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,7; -9,78</t>
+          <t>-87,68; -13,72</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,66</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,81</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,01</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-3,69</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,66</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-2,27</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-3,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 1,96</t>
+          <t>-5,9; 2,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 1,48</t>
+          <t>-7,62; -0,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 0,7</t>
+          <t>-6,99; 1,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 2,55</t>
+          <t>-7,32; 1,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; -0,18</t>
+          <t>-7,71; 1,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,82</t>
+          <t>-8,52; 0,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,81</t>
+          <t>-5,34; 0,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -0,64</t>
+          <t>-6,63; -0,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,08</t>
+          <t>-6,61; -0,19</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-32,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-68,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-50,07%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-44,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-47,28%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-58,1%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-32,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-68,81%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-48,97%</t>
+          <t>-58,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-53,82%</t>
+          <t>-54,39%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,88; 82,07</t>
+          <t>-79,52; 110,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,93; 48,52</t>
+          <t>-100,0; 10,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-91,83; 42,57</t>
+          <t>-88,47; 79,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-78,78; 97,69</t>
+          <t>-81,73; 68,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-92,68; 39,68</t>
+          <t>-83,4; 54,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,1; 98,23</t>
+          <t>-90,2; 47,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,76; 24,36</t>
+          <t>-71,24; 16,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,61; -8,99</t>
+          <t>-81,76; -3,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,44; 7,1</t>
+          <t>-81,67; 4,58</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,99</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,05</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,46</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-5,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>-2,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 4,76</t>
+          <t>-8,03; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 3,31</t>
+          <t>-7,72; 2,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -0,8</t>
+          <t>-5,15; 12,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 0,09</t>
+          <t>-7,38; 4,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,23</t>
+          <t>-7,78; 3,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 10,8</t>
+          <t>-10,77; -1,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 1,44</t>
+          <t>-6,65; 1,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 1,82</t>
+          <t>-6,05; 1,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,52</t>
+          <t>-5,89; 4,92</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-68,66%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-45,55%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-23,34%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-32,12%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-81,54%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-68,66%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-45,55%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>-83,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-41,13%</t>
+          <t>-39,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,65; 176,85</t>
+          <t>-100,0; 272,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-85,52; 127,88</t>
+          <t>-100,0; 145,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 33,37</t>
+          <t>-87,56; 921,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,48</t>
+          <t>-79,85; 163,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 126,35</t>
+          <t>-82,08; 156,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-92,29; 847,17</t>
+          <t>-100,0; 18,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,17; 61,84</t>
+          <t>-81,73; 47,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,13; 78,85</t>
+          <t>-78,28; 67,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-86,36; 166,11</t>
+          <t>-86,39; 186,41</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,09</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,01</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,45</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,52</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,65</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 7,42</t>
+          <t>-1,04; 8,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,99</t>
+          <t>-3,55; 1,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,97</t>
+          <t>-2,02; 6,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,94</t>
+          <t>-1,74; 7,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,91</t>
+          <t>-5,14; 1,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 6,67</t>
+          <t>-5,15; 1,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,38</t>
+          <t>-0,03; 6,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,05</t>
+          <t>-3,42; 1,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,22</t>
+          <t>-2,34; 3,02</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>146,56%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-36,57%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>97,23%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-60,25%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-65,23%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>146,56%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-36,57%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>-63,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>-56,62; —</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>-76,22; —</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-61,82; —</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-56,34; 1063,37</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-68,48; —</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 550,29</t>
+          <t>-17,67; 519,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-92,17; 253,71</t>
+          <t>-91,17; 237,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,59; 342,57</t>
+          <t>-68,31; 298,41</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,89</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,95</t>
+          <t>-3,66; 1,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,79</t>
+          <t>-4,45; 0,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -1,18</t>
+          <t>-4,01; 1,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,4</t>
+          <t>-4,22; 1,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,02</t>
+          <t>-4,65; 0,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,69</t>
+          <t>-6,29; -1,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,57</t>
+          <t>-2,95; 0,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,23</t>
+          <t>-3,69; -0,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,51</t>
+          <t>-3,99; -0,33</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-22,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-45,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-30,27%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-26,21%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-33,18%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-61,23%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-22,0%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-45,24%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-30,05%</t>
+          <t>-61,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-45,7%</t>
+          <t>-46,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 24,26</t>
+          <t>-58,29; 41,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-62,76; 18,43</t>
+          <t>-72,3; 10,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,15; -26,09</t>
+          <t>-65,87; 53,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 46,11</t>
+          <t>-58,01; 31,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 2,91</t>
+          <t>-63,25; 19,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 53,05</t>
+          <t>-82,04; -29,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 13,74</t>
+          <t>-48,09; 13,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,15; -3,77</t>
+          <t>-59,72; -4,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -6,83</t>
+          <t>-65,62; -5,19</t>
         </is>
       </c>
     </row>
